--- a/public/import_guru_siswa/template_guru.xlsx
+++ b/public/import_guru_siswa/template_guru.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SIMPEL-5\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\SIMPEL-5\public\import_guru_siswa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D18649-3907-4A88-8E7C-B8EC64F301EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0882A06D-960C-481F-ABF1-71A9B4FC0F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B5C1236F-2DC1-4DEB-9CB8-AC0626038A09}"/>
   </bookViews>
@@ -57,10 +57,10 @@
     <t>dosen6@gmail.com</t>
   </si>
   <si>
-    <t>Guru 5</t>
-  </si>
-  <si>
-    <t>Guru 6</t>
+    <t>Guru 5 import</t>
+  </si>
+  <si>
+    <t>Guru 6 import</t>
   </si>
 </sst>
 </file>
